--- a/dev/양식.xlsx
+++ b/dev/양식.xlsx
@@ -530,7 +530,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="9.5" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="31.8" customWidth="1" min="3" max="3"/>
     <col width="31.8" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
